--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69968EC9-7D60-4FB3-8866-BCF2BB01A7BB}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D07F768-3304-41CF-900A-D4A60DD13256}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
   <si>
     <t>Stage</t>
   </si>
@@ -168,6 +168,30 @@
   </si>
   <si>
     <t>Clément Braz Afonso</t>
+  </si>
+  <si>
+    <t>Anthon Charmig</t>
+  </si>
+  <si>
+    <t>Henri-François Renard-Haquin</t>
+  </si>
+  <si>
+    <t>Vlad Van Mechelen</t>
+  </si>
+  <si>
+    <t>Raúl García Pierna</t>
+  </si>
+  <si>
+    <t>Benjamin Thomas</t>
+  </si>
+  <si>
+    <t>Jordan Jegat</t>
+  </si>
+  <si>
+    <t>Finn Fisher-Black</t>
+  </si>
+  <si>
+    <t>Maxim Van Gils</t>
   </si>
 </sst>
 </file>
@@ -547,35 +571,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="26" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -670,7 +694,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46180</v>
       </c>
@@ -765,15 +789,102 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46181</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46182</v>
       </c>
@@ -781,7 +892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46183</v>
       </c>
@@ -789,7 +900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46184</v>
       </c>
@@ -797,7 +908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46185</v>
       </c>
@@ -805,7 +916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46186</v>
       </c>
@@ -813,7 +924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46187</v>
       </c>
@@ -829,6 +940,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1063,15 +1183,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1091,6 +1202,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1105,14 +1224,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D07F768-3304-41CF-900A-D4A60DD13256}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7879657B-B7C3-4A84-A5FF-811A8B71A352}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
   <si>
     <t>Stage</t>
   </si>
@@ -192,6 +192,24 @@
   </si>
   <si>
     <t>Maxim Van Gils</t>
+  </si>
+  <si>
+    <t>Matteo Jorgenson</t>
+  </si>
+  <si>
+    <t>Juan Ayuso</t>
+  </si>
+  <si>
+    <t>Mattias Skjelmose</t>
+  </si>
+  <si>
+    <t>Jørgen Nordhagen</t>
+  </si>
+  <si>
+    <t>Bruno Armirail</t>
+  </si>
+  <si>
+    <t>Carlos Rodríguez</t>
   </si>
 </sst>
 </file>
@@ -891,6 +909,63 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" t="s">
+        <v>55</v>
+      </c>
+      <c r="T4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -940,15 +1015,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1183,6 +1249,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1202,14 +1277,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1224,6 +1291,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7879657B-B7C3-4A84-A5FF-811A8B71A352}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB6B241F-F4A1-4596-A203-6C0CB0E92541}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
   <si>
     <t>Stage</t>
   </si>
@@ -210,6 +210,36 @@
   </si>
   <si>
     <t>Carlos Rodríguez</t>
+  </si>
+  <si>
+    <t>Team Visma | Lease a Bike</t>
+  </si>
+  <si>
+    <t>Netcompany INEOS</t>
+  </si>
+  <si>
+    <t>EF Education - EasyPost</t>
+  </si>
+  <si>
+    <t>Lidl - Trek</t>
+  </si>
+  <si>
+    <t>Red Bull - BORA - hansgrohe</t>
+  </si>
+  <si>
+    <t>Decathlon CMA CGM Team</t>
+  </si>
+  <si>
+    <t>Movistar Team</t>
+  </si>
+  <si>
+    <t>Team Jayco AlUla</t>
+  </si>
+  <si>
+    <t>UAE Team Emirates - XRG</t>
+  </si>
+  <si>
+    <t>Bahrain - Victorious</t>
   </si>
 </sst>
 </file>
@@ -909,6 +939,36 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
       <c r="M4" t="s">
         <v>31</v>
       </c>
@@ -1015,6 +1075,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1249,15 +1318,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1277,6 +1337,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1291,14 +1359,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB6B241F-F4A1-4596-A203-6C0CB0E92541}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BCB3056-7AB8-4DDB-8AF1-9073B208C3BC}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
   <si>
     <t>Stage</t>
   </si>
@@ -240,6 +240,30 @@
   </si>
   <si>
     <t>Bahrain - Victorious</t>
+  </si>
+  <si>
+    <t>Quinn Simmons</t>
+  </si>
+  <si>
+    <t>Mattéo Vercher</t>
+  </si>
+  <si>
+    <t>Marco Frigo</t>
+  </si>
+  <si>
+    <t>Andreas Kron</t>
+  </si>
+  <si>
+    <t>Lars Craps</t>
+  </si>
+  <si>
+    <t>Jan Castellon</t>
+  </si>
+  <si>
+    <t>Pablo Castrillo</t>
+  </si>
+  <si>
+    <t>Paul Seixas</t>
   </si>
 </sst>
 </file>
@@ -1034,6 +1058,93 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>53</v>
+      </c>
+      <c r="R5" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T5" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1075,15 +1186,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1318,6 +1420,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1337,14 +1448,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1359,6 +1462,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BCB3056-7AB8-4DDB-8AF1-9073B208C3BC}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D898041E-CBB9-48AC-ACC6-69F362104CA2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
   <si>
     <t>Stage</t>
   </si>
@@ -264,6 +264,30 @@
   </si>
   <si>
     <t>Paul Seixas</t>
+  </si>
+  <si>
+    <t>Wout Van Aert</t>
+  </si>
+  <si>
+    <t>Hugo Hofstetter</t>
+  </si>
+  <si>
+    <t>Phil Bauhaus</t>
+  </si>
+  <si>
+    <t>Vito Braet</t>
+  </si>
+  <si>
+    <t>Dorian Godon</t>
+  </si>
+  <si>
+    <t>Henri Uhlig</t>
+  </si>
+  <si>
+    <t>Bryan Coquard</t>
+  </si>
+  <si>
+    <t>Matteo Trentin</t>
   </si>
 </sst>
 </file>
@@ -1153,6 +1177,93 @@
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" t="s">
+        <v>55</v>
+      </c>
+      <c r="T6" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" t="s">
+        <v>33</v>
+      </c>
+      <c r="V6" t="s">
+        <v>75</v>
+      </c>
+      <c r="W6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1186,6 +1297,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1420,15 +1540,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1448,6 +1559,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1462,14 +1581,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D898041E-CBB9-48AC-ACC6-69F362104CA2}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABCC7FA9-70EC-473D-A9A3-E1096950FD1A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>Stage</t>
   </si>
@@ -288,6 +288,30 @@
   </si>
   <si>
     <t>Matteo Trentin</t>
+  </si>
+  <si>
+    <t>Tobias Halland Johannessen</t>
+  </si>
+  <si>
+    <t>Pablo Torres</t>
+  </si>
+  <si>
+    <t>Yannis Voisard</t>
+  </si>
+  <si>
+    <t>Cristián Rodríguez</t>
+  </si>
+  <si>
+    <t>Lennart Jasch</t>
+  </si>
+  <si>
+    <t>Guillaume Martin</t>
+  </si>
+  <si>
+    <t>José Félix Parra</t>
+  </si>
+  <si>
+    <t>Isaac Del Toro</t>
   </si>
 </sst>
 </file>
@@ -671,28 +695,32 @@
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1271,6 +1299,93 @@
       </c>
       <c r="B7">
         <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" t="s">
+        <v>90</v>
+      </c>
+      <c r="S7" t="s">
+        <v>75</v>
+      </c>
+      <c r="T7" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W7" t="s">
+        <v>41</v>
+      </c>
+      <c r="X7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -1297,15 +1412,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1540,6 +1646,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1559,14 +1674,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1581,6 +1688,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABCC7FA9-70EC-473D-A9A3-E1096950FD1A}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEB88CE9-6438-4EA6-8205-42B69C3B85E8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
   <si>
     <t>Stage</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>Isaac Del Toro</t>
+  </si>
+  <si>
+    <t>Cian Uijtdebroeks</t>
   </si>
 </sst>
 </file>
@@ -691,39 +694,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -818,7 +821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46180</v>
       </c>
@@ -913,7 +916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46181</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46182</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46183</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46184</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46185</v>
       </c>
@@ -1388,15 +1391,102 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46186</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T8" t="s">
+        <v>92</v>
+      </c>
+      <c r="U8" t="s">
+        <v>87</v>
+      </c>
+      <c r="V8" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" t="s">
+        <v>41</v>
+      </c>
+      <c r="X8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46187</v>
       </c>
@@ -1412,6 +1502,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1646,15 +1745,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1674,6 +1764,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1688,14 +1786,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent.sharepoint.com/sites/acctmgmt/Shared Documents/Daniel/Cycling/2026/2026 Crit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEB88CE9-6438-4EA6-8205-42B69C3B85E8}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{B0B98796-A569-48D3-947C-B34FB1775981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30D6C002-E9C3-4223-BBFD-F1E0C6D61848}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="93">
   <si>
     <t>Stage</t>
   </si>
@@ -1493,6 +1493,93 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" t="s">
+        <v>92</v>
+      </c>
+      <c r="T9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U9" t="s">
+        <v>90</v>
+      </c>
+      <c r="V9" t="s">
+        <v>89</v>
+      </c>
+      <c r="W9" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1502,15 +1589,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C440F6B30AEFA49AEE9581EA6D48B46" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df4afd50c0c053b6273c7f05e5bb03ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="af4a67e0-1abd-4649-84fb-fd653100e8b2" xmlns:ns3="7175da68-f620-4bd3-83fc-e7e6d9b5dad2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a657d4be930610df655a4f1deb8c006" ns2:_="" ns3:_="">
     <xsd:import namespace="af4a67e0-1abd-4649-84fb-fd653100e8b2"/>
@@ -1745,6 +1823,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1764,14 +1851,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213EC4F2-EDAE-402D-AA6A-E64546B6E020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1786,6 +1865,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9628637F-4968-4A1B-95CC-4E0244695FE5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
